--- a/dietitian_forms/007_food_consumption_survey--dietitian_forms.xlsx
+++ b/dietitian_forms/007_food_consumption_survey--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'less_than_once_a_week',_'label':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'Less than once a week', 'label': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'1-2_times_a_week',_'label':_'1-2_times_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': '1-2 times a week', 'label': '1-2 times a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'3-4_times_a_week',_'label':_'3-4_times_a_week'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': '3-4 times a week', 'label': '3-4 times a week'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'5_or_more_times_a_week',_'label':_'5_or_more_times_a_week'}</t>
+          <t>5_or_more_times_a_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': '5 or more times a week', 'label': '5 or more times a week'}</t>
+          <t>5 or more times a week</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_51,_'name':_'fast_food',_'label':_'fast_food'}</t>
+          <t>fast_food</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 51, 'name': 'Fast Food', 'label': 'Fast Food'}</t>
+          <t>Fast Food</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'fruits',_'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Fruits', 'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'vegetables',_'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Vegetables', 'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'meat',_'label':_'meat'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Meat', 'label': 'Meat'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'dairy',_'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Dairy', 'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'baked_goods',_'label':_'baked_goods'}</t>
+          <t>baked_goods</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Baked Goods', 'label': 'Baked Goods'}</t>
+          <t>Baked Goods</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'sweets',_'label':_'sweets'}</t>
+          <t>sweets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Sweets', 'label': 'Sweets'}</t>
+          <t>Sweets</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'fruits',_'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Fruits', 'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'vegetables',_'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Vegetables', 'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'meat',_'label':_'meat'}</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Meat', 'label': 'Meat'}</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'dairy',_'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Dairy', 'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_61,_'name':_'baked_goods',_'label':_'baked_goods'}</t>
+          <t>baked_goods</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 61, 'name': 'Baked Goods', 'label': 'Baked Goods'}</t>
+          <t>Baked Goods</t>
         </is>
       </c>
     </row>
